--- a/files/excel-mastery-ch3.xlsx
+++ b/files/excel-mastery-ch3.xlsx
@@ -547,7 +547,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -555,8 +555,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -653,9 +656,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -710,21 +710,12 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -737,29 +728,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -875,189 +845,295 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -1065,89 +1141,27 @@
     <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準 2" xfId="2"/>
+    <cellStyle name="パーセント" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1587,256 +1601,256 @@
   <dimension ref="B2:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="18" customWidth="1" style="158" min="4" max="4"/>
-    <col width="40" customWidth="1" style="158" min="5" max="5"/>
-    <col width="16" customWidth="1" style="158" min="6" max="6"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
-      <c r="B2" s="75" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>00_Index ― 目次・ファイル概要</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="158"/>
-    <row r="4" ht="13.5" customHeight="1" s="158">
+    <row r="3" ht="13.5" customHeight="1"/>
+    <row r="4" ht="13.5" customHeight="1">
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>このファイルの目的：施設別の月次売上を、元データから集計してKPIを出力する実績集計ブック（入力→計算→出力→検証を分離）。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1" s="158">
-      <c r="D5" s="77" t="inlineStr">
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>更新日 / 前提の要約</t>
         </is>
       </c>
-      <c r="E5" s="78" t="n"/>
-      <c r="F5" s="78" t="n"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" s="158"/>
-    <row r="7" ht="13.5" customHeight="1" s="158">
-      <c r="D7" s="168" t="inlineStr">
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+    </row>
+    <row r="6" ht="13.5" customHeight="1"/>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="E7" s="168" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="F7" s="168" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>更新日</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
-      <c r="D8" s="80" t="inlineStr">
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="D8" s="69" t="inlineStr">
         <is>
           <t>対象期間</t>
         </is>
       </c>
-      <c r="E8" s="80" t="inlineStr">
+      <c r="E8" s="69" t="inlineStr">
         <is>
           <t>2026年7月〜8月</t>
         </is>
       </c>
-      <c r="F8" s="88" t="inlineStr">
+      <c r="F8" s="77" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
-      <c r="D9" s="83" t="inlineStr">
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="72" t="inlineStr">
         <is>
           <t>消費税率</t>
         </is>
       </c>
-      <c r="E9" s="83" t="inlineStr">
+      <c r="E9" s="72" t="inlineStr">
         <is>
           <t>10%（税抜集計）</t>
         </is>
       </c>
-      <c r="F9" s="90" t="inlineStr">
+      <c r="F9" s="79" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
-      <c r="D10" s="85" t="inlineStr">
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="D10" s="74" t="inlineStr">
         <is>
           <t>対象施設</t>
         </is>
       </c>
-      <c r="E10" s="85" t="inlineStr">
+      <c r="E10" s="74" t="inlineStr">
         <is>
           <t>西伊豆・熱海（Masterシート参照）</t>
         </is>
       </c>
-      <c r="F10" s="94" t="inlineStr">
+      <c r="F10" s="83" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1" s="158"/>
-    <row r="12" ht="13.5" customHeight="1" s="158"/>
-    <row r="13" ht="13.5" customHeight="1" s="158"/>
-    <row r="14" ht="13.5" customHeight="1" s="158">
-      <c r="D14" s="77" t="inlineStr">
+    <row r="11" ht="13.5" customHeight="1"/>
+    <row r="12" ht="13.5" customHeight="1"/>
+    <row r="13" ht="13.5" customHeight="1"/>
+    <row r="14" ht="13.5" customHeight="1">
+      <c r="D14" s="66" t="inlineStr">
         <is>
           <t>シート構成</t>
         </is>
       </c>
-      <c r="E14" s="78" t="n"/>
-      <c r="F14" s="78" t="n"/>
-    </row>
-    <row r="15" ht="13.5" customHeight="1" s="158"/>
-    <row r="16" ht="13.5" customHeight="1" s="158">
-      <c r="D16" s="168" t="inlineStr">
+      <c r="E14" s="67" t="n"/>
+      <c r="F14" s="67" t="n"/>
+    </row>
+    <row r="15" ht="13.5" customHeight="1"/>
+    <row r="16" ht="13.5" customHeight="1">
+      <c r="D16" s="68" t="inlineStr">
         <is>
           <t>シート</t>
         </is>
       </c>
-      <c r="E16" s="168" t="inlineStr">
+      <c r="E16" s="68" t="inlineStr">
         <is>
           <t>役割</t>
         </is>
       </c>
-      <c r="F16" s="168" t="inlineStr">
+      <c r="F16" s="68" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1" s="158">
-      <c r="D17" s="80" t="inlineStr">
+    <row r="17" ht="13.5" customHeight="1">
+      <c r="D17" s="69" t="inlineStr">
         <is>
           <t>00_Index</t>
         </is>
       </c>
-      <c r="E17" s="80" t="inlineStr">
+      <c r="E17" s="69" t="inlineStr">
         <is>
           <t>目次・目的・更新日・前提の要約</t>
         </is>
       </c>
-      <c r="F17" s="88" t="inlineStr">
+      <c r="F17" s="77" t="inlineStr">
         <is>
           <t>案内</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1" s="158">
-      <c r="D18" s="83" t="inlineStr">
+    <row r="18" ht="13.5" customHeight="1">
+      <c r="D18" s="72" t="inlineStr">
         <is>
           <t>01_Assumption</t>
         </is>
       </c>
-      <c r="E18" s="83" t="inlineStr">
+      <c r="E18" s="72" t="inlineStr">
         <is>
           <t>前提条件・置き値（青字入力を集約）</t>
         </is>
       </c>
-      <c r="F18" s="90" t="inlineStr">
+      <c r="F18" s="79" t="inlineStr">
         <is>
           <t>入力</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="13.5" customHeight="1" s="158">
-      <c r="D19" s="83" t="inlineStr">
+    <row r="19" ht="13.5" customHeight="1">
+      <c r="D19" s="72" t="inlineStr">
         <is>
           <t>02_RawData</t>
         </is>
       </c>
-      <c r="E19" s="83" t="inlineStr">
+      <c r="E19" s="72" t="inlineStr">
         <is>
           <t>加工前の元データ（触らない）</t>
         </is>
       </c>
-      <c r="F19" s="90" t="inlineStr">
+      <c r="F19" s="79" t="inlineStr">
         <is>
           <t>元データ</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="158">
-      <c r="D20" s="83" t="inlineStr">
+    <row r="20" ht="13.5" customHeight="1">
+      <c r="D20" s="72" t="inlineStr">
         <is>
           <t>03_Master</t>
         </is>
       </c>
-      <c r="E20" s="83" t="inlineStr">
+      <c r="E20" s="72" t="inlineStr">
         <is>
           <t>施設・OTAなどのマスタ</t>
         </is>
       </c>
-      <c r="F20" s="90" t="inlineStr">
+      <c r="F20" s="79" t="inlineStr">
         <is>
           <t>マスタ</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="13.5" customHeight="1" s="158">
-      <c r="D21" s="83" t="inlineStr">
+    <row r="21" ht="13.5" customHeight="1">
+      <c r="D21" s="72" t="inlineStr">
         <is>
           <t>04_Calculation</t>
         </is>
       </c>
-      <c r="E21" s="83" t="inlineStr">
+      <c r="E21" s="72" t="inlineStr">
         <is>
           <t>集計・計算ロジック</t>
         </is>
       </c>
-      <c r="F21" s="90" t="inlineStr">
+      <c r="F21" s="79" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1" s="158">
-      <c r="D22" s="83" t="inlineStr">
+    <row r="22" ht="13.5" customHeight="1">
+      <c r="D22" s="72" t="inlineStr">
         <is>
           <t>05_Output</t>
         </is>
       </c>
-      <c r="E22" s="83" t="inlineStr">
+      <c r="E22" s="72" t="inlineStr">
         <is>
           <t>結果表・KPI</t>
         </is>
       </c>
-      <c r="F22" s="90" t="inlineStr">
+      <c r="F22" s="79" t="inlineStr">
         <is>
           <t>出力</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1" s="158">
-      <c r="D23" s="85" t="inlineStr">
+    <row r="23" ht="13.5" customHeight="1">
+      <c r="D23" s="74" t="inlineStr">
         <is>
           <t>06_Check</t>
         </is>
       </c>
-      <c r="E23" s="85" t="inlineStr">
+      <c r="E23" s="74" t="inlineStr">
         <is>
           <t>エラーチェック・整合性確認</t>
         </is>
       </c>
-      <c r="F23" s="94" t="inlineStr">
+      <c r="F23" s="83" t="inlineStr">
         <is>
           <t>検証</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1" s="158"/>
-    <row r="25" ht="13.5" customHeight="1" s="158"/>
+    <row r="24" ht="13.5" customHeight="1"/>
+    <row r="25" ht="13.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1851,102 +1865,102 @@
   <dimension ref="B2:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="15.36328125" bestFit="1" customWidth="1" style="158" min="4" max="4"/>
-    <col width="14" customWidth="1" style="158" min="5" max="5"/>
-    <col width="10" customWidth="1" style="158" min="6" max="6"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="15.36328125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
-      <c r="B2" s="75" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>01_Assumption ― 前提条件（青字が入力）</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="158"/>
-    <row r="4" ht="13.5" customHeight="1" s="158"/>
-    <row r="5" ht="13.5" customHeight="1" s="158">
-      <c r="D5" s="77" t="inlineStr">
+    <row r="3" ht="13.5" customHeight="1"/>
+    <row r="4" ht="13.5" customHeight="1"/>
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>前提・置き値</t>
         </is>
       </c>
-      <c r="E5" s="78" t="n"/>
-      <c r="F5" s="78" t="n"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" s="158"/>
-    <row r="7" ht="13.5" customHeight="1" s="158">
-      <c r="D7" s="168" t="inlineStr">
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+    </row>
+    <row r="6" ht="13.5" customHeight="1"/>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="E7" s="168" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>値</t>
         </is>
       </c>
-      <c r="F7" s="168" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
-      <c r="D8" s="124" t="inlineStr">
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="D8" s="109" t="inlineStr">
         <is>
           <t>消費税率</t>
         </is>
       </c>
-      <c r="E8" s="189" t="n">
+      <c r="E8" s="191" t="n">
         <v>0.1</v>
       </c>
-      <c r="F8" s="168" t="n"/>
-    </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
-      <c r="D9" s="124" t="inlineStr">
+      <c r="F8" s="68" t="n"/>
+    </row>
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="109" t="inlineStr">
         <is>
           <t>集計対象月・開始</t>
         </is>
       </c>
-      <c r="E9" s="188" t="n">
+      <c r="E9" s="166" t="n">
         <v>7</v>
       </c>
-      <c r="F9" s="168" t="inlineStr">
+      <c r="F9" s="68" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
-      <c r="D10" s="124" t="inlineStr">
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="D10" s="109" t="inlineStr">
         <is>
           <t>集計対象月・終了</t>
         </is>
       </c>
-      <c r="E10" s="188" t="n">
+      <c r="E10" s="166" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="168" t="inlineStr">
+      <c r="F10" s="68" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1" s="158">
-      <c r="D11" s="124" t="inlineStr">
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="D11" s="109" t="inlineStr">
         <is>
           <t>目標稼働率</t>
         </is>
       </c>
-      <c r="E11" s="189" t="n">
+      <c r="E11" s="191" t="n">
         <v>0.7</v>
       </c>
-      <c r="F11" s="168" t="n"/>
-    </row>
-    <row r="12" ht="13.5" customHeight="1" s="158"/>
-    <row r="13" ht="13.5" customHeight="1" s="158"/>
+      <c r="F11" s="68" t="n"/>
+    </row>
+    <row r="12" ht="13.5" customHeight="1"/>
+    <row r="13" ht="13.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1961,338 +1975,338 @@
   <dimension ref="B2:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="10" customWidth="1" style="158" min="4" max="5"/>
-    <col width="7" customWidth="1" style="158" min="6" max="6"/>
-    <col width="14" customWidth="1" style="158" min="7" max="7"/>
-    <col width="9" customWidth="1" style="158" min="8" max="8"/>
-    <col width="14" customWidth="1" style="158" min="9" max="9"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="10" customWidth="1" min="4" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
-      <c r="B2" s="75" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>02_RawData ― 元データ（加工しない）</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="158"/>
-    <row r="4" ht="13.5" customHeight="1" s="158">
+    <row r="3" ht="13.5" customHeight="1"/>
+    <row r="4" ht="13.5" customHeight="1">
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>このシートは元データ。数式や加工を入れず、そのまま保持する。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1" s="158">
-      <c r="D5" s="77" t="inlineStr">
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>元データ（予約明細）</t>
         </is>
       </c>
-      <c r="E5" s="78" t="n"/>
-      <c r="F5" s="78" t="n"/>
-      <c r="G5" s="78" t="n"/>
-      <c r="H5" s="78" t="n"/>
-      <c r="I5" s="78" t="n"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" s="158"/>
-    <row r="7" ht="13.5" customHeight="1" s="158">
-      <c r="D7" s="169" t="inlineStr">
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+      <c r="G5" s="67" t="n"/>
+      <c r="H5" s="67" t="n"/>
+      <c r="I5" s="67" t="n"/>
+    </row>
+    <row r="6" ht="13.5" customHeight="1"/>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="D7" s="148" t="inlineStr">
         <is>
           <t>予約ID</t>
         </is>
       </c>
-      <c r="E7" s="169" t="inlineStr">
+      <c r="E7" s="148" t="inlineStr">
         <is>
           <t>施設</t>
         </is>
       </c>
-      <c r="F7" s="169" t="inlineStr">
+      <c r="F7" s="148" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="G7" s="169" t="inlineStr">
+      <c r="G7" s="148" t="inlineStr">
         <is>
           <t>客室タイプ</t>
         </is>
       </c>
-      <c r="H7" s="169" t="inlineStr">
+      <c r="H7" s="148" t="inlineStr">
         <is>
           <t>泊数</t>
         </is>
       </c>
-      <c r="I7" s="169" t="inlineStr">
+      <c r="I7" s="148" t="inlineStr">
         <is>
           <t>売上税抜(円)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
-      <c r="D8" s="169" t="inlineStr">
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="D8" s="148" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="E8" s="169" t="inlineStr">
+      <c r="E8" s="148" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="F8" s="169" t="n">
+      <c r="F8" s="148" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="169" t="inlineStr">
+      <c r="G8" s="148" t="inlineStr">
         <is>
           <t>スイート</t>
         </is>
       </c>
-      <c r="H8" s="169" t="n">
+      <c r="H8" s="148" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="169" t="n">
+      <c r="I8" s="148" t="n">
         <v>160000</v>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
-      <c r="D9" s="169" t="inlineStr">
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="148" t="inlineStr">
         <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="E9" s="169" t="inlineStr">
+      <c r="E9" s="148" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="F9" s="169" t="n">
+      <c r="F9" s="148" t="n">
         <v>7</v>
       </c>
-      <c r="G9" s="169" t="inlineStr">
+      <c r="G9" s="148" t="inlineStr">
         <is>
           <t>スタンダード</t>
         </is>
       </c>
-      <c r="H9" s="169" t="n">
+      <c r="H9" s="148" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="169" t="n">
+      <c r="I9" s="148" t="n">
         <v>108000</v>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
-      <c r="D10" s="169" t="inlineStr">
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="D10" s="148" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="E10" s="169" t="inlineStr">
+      <c r="E10" s="148" t="inlineStr">
         <is>
           <t>熱海</t>
         </is>
       </c>
-      <c r="F10" s="169" t="n">
+      <c r="F10" s="148" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="169" t="inlineStr">
+      <c r="G10" s="148" t="inlineStr">
         <is>
           <t>スタンダード</t>
         </is>
       </c>
-      <c r="H10" s="169" t="n">
+      <c r="H10" s="148" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="169" t="n">
+      <c r="I10" s="148" t="n">
         <v>72000</v>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1" s="158">
-      <c r="D11" s="169" t="inlineStr">
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="D11" s="148" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="E11" s="169" t="inlineStr">
+      <c r="E11" s="148" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="F11" s="169" t="n">
+      <c r="F11" s="148" t="n">
         <v>8</v>
       </c>
-      <c r="G11" s="169" t="inlineStr">
+      <c r="G11" s="148" t="inlineStr">
         <is>
           <t>スイート</t>
         </is>
       </c>
-      <c r="H11" s="169" t="n">
+      <c r="H11" s="148" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="169" t="n">
+      <c r="I11" s="148" t="n">
         <v>180000</v>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1" s="158">
-      <c r="D12" s="169" t="inlineStr">
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="D12" s="148" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="E12" s="169" t="inlineStr">
+      <c r="E12" s="148" t="inlineStr">
         <is>
           <t>熱海</t>
         </is>
       </c>
-      <c r="F12" s="169" t="n">
+      <c r="F12" s="148" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="169" t="inlineStr">
+      <c r="G12" s="148" t="inlineStr">
         <is>
           <t>スイート</t>
         </is>
       </c>
-      <c r="H12" s="169" t="n">
+      <c r="H12" s="148" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="169" t="n">
+      <c r="I12" s="148" t="n">
         <v>95000</v>
       </c>
     </row>
-    <row r="13" ht="13.5" customHeight="1" s="158">
-      <c r="D13" s="169" t="inlineStr">
+    <row r="13" ht="13.5" customHeight="1">
+      <c r="D13" s="148" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="E13" s="169" t="inlineStr">
+      <c r="E13" s="148" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="F13" s="169" t="n">
+      <c r="F13" s="148" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="169" t="inlineStr">
+      <c r="G13" s="148" t="inlineStr">
         <is>
           <t>スタンダード</t>
         </is>
       </c>
-      <c r="H13" s="169" t="n">
+      <c r="H13" s="148" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="169" t="n">
+      <c r="I13" s="148" t="n">
         <v>36000</v>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1" s="158">
-      <c r="D14" s="169" t="inlineStr">
+    <row r="14" ht="13.5" customHeight="1">
+      <c r="D14" s="148" t="inlineStr">
         <is>
           <t>R007</t>
         </is>
       </c>
-      <c r="E14" s="169" t="inlineStr">
+      <c r="E14" s="148" t="inlineStr">
         <is>
           <t>熱海</t>
         </is>
       </c>
-      <c r="F14" s="169" t="n">
+      <c r="F14" s="148" t="n">
         <v>8</v>
       </c>
-      <c r="G14" s="169" t="inlineStr">
+      <c r="G14" s="148" t="inlineStr">
         <is>
           <t>スタンダード</t>
         </is>
       </c>
-      <c r="H14" s="169" t="n">
+      <c r="H14" s="148" t="n">
         <v>4</v>
       </c>
-      <c r="I14" s="169" t="n">
+      <c r="I14" s="148" t="n">
         <v>152000</v>
       </c>
     </row>
-    <row r="15" ht="13.5" customHeight="1" s="158">
-      <c r="D15" s="169" t="inlineStr">
+    <row r="15" ht="13.5" customHeight="1">
+      <c r="D15" s="148" t="inlineStr">
         <is>
           <t>R008</t>
         </is>
       </c>
-      <c r="E15" s="169" t="inlineStr">
+      <c r="E15" s="148" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="F15" s="169" t="n">
+      <c r="F15" s="148" t="n">
         <v>8</v>
       </c>
-      <c r="G15" s="169" t="inlineStr">
+      <c r="G15" s="148" t="inlineStr">
         <is>
           <t>スタンダード</t>
         </is>
       </c>
-      <c r="H15" s="169" t="n">
+      <c r="H15" s="148" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="169" t="n">
+      <c r="I15" s="148" t="n">
         <v>74000</v>
       </c>
     </row>
-    <row r="16" ht="13.5" customHeight="1" s="158">
-      <c r="D16" s="169" t="inlineStr">
+    <row r="16" ht="13.5" customHeight="1">
+      <c r="D16" s="148" t="inlineStr">
         <is>
           <t>R009</t>
         </is>
       </c>
-      <c r="E16" s="169" t="inlineStr">
+      <c r="E16" s="148" t="inlineStr">
         <is>
           <t>熱海</t>
         </is>
       </c>
-      <c r="F16" s="169" t="n">
+      <c r="F16" s="148" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="169" t="inlineStr">
+      <c r="G16" s="148" t="inlineStr">
         <is>
           <t>スイート</t>
         </is>
       </c>
-      <c r="H16" s="169" t="n">
+      <c r="H16" s="148" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="169" t="n">
+      <c r="I16" s="148" t="n">
         <v>92000</v>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1" s="158">
-      <c r="D17" s="169" t="inlineStr">
+    <row r="17" ht="13.5" customHeight="1">
+      <c r="D17" s="148" t="inlineStr">
         <is>
           <t>R010</t>
         </is>
       </c>
-      <c r="E17" s="169" t="inlineStr">
+      <c r="E17" s="148" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="F17" s="169" t="n">
+      <c r="F17" s="148" t="n">
         <v>8</v>
       </c>
-      <c r="G17" s="169" t="inlineStr">
+      <c r="G17" s="148" t="inlineStr">
         <is>
           <t>スイート</t>
         </is>
       </c>
-      <c r="H17" s="169" t="n">
+      <c r="H17" s="148" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="169" t="n">
+      <c r="I17" s="148" t="n">
         <v>270000</v>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1" s="158"/>
-    <row r="19" ht="13.5" customHeight="1" s="158"/>
-    <row r="20" ht="13.5" customHeight="1" s="158"/>
-    <row r="21" ht="13.5" customHeight="1" s="158"/>
+    <row r="18" ht="13.5" customHeight="1"/>
+    <row r="19" ht="13.5" customHeight="1"/>
+    <row r="20" ht="13.5" customHeight="1"/>
+    <row r="21" ht="13.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2307,98 +2321,98 @@
   <dimension ref="B2:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="12" customWidth="1" style="158" min="4" max="5"/>
-    <col width="10" customWidth="1" style="158" min="6" max="6"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="12" customWidth="1" min="4" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
-      <c r="B2" s="75" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>03_Master ― マスタ</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="158"/>
-    <row r="4" ht="13.5" customHeight="1" s="158">
+    <row r="3" ht="13.5" customHeight="1"/>
+    <row r="4" ht="13.5" customHeight="1">
       <c r="D4" s="3" t="n"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1" s="158">
-      <c r="D5" s="77" t="inlineStr">
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>施設マスタ</t>
         </is>
       </c>
-      <c r="E5" s="78" t="n"/>
-      <c r="F5" s="78" t="n"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" s="158"/>
-    <row r="7" ht="13.5" customHeight="1" s="158">
-      <c r="D7" s="168" t="inlineStr">
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+    </row>
+    <row r="6" ht="13.5" customHeight="1"/>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>施設</t>
         </is>
       </c>
-      <c r="E7" s="168" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>客室数(室)</t>
         </is>
       </c>
-      <c r="F7" s="168" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>エリア</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
-      <c r="D8" s="184" t="inlineStr">
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="D8" s="162" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="E8" s="185" t="n">
+      <c r="E8" s="163" t="n">
         <v>20</v>
       </c>
-      <c r="F8" s="186" t="inlineStr">
+      <c r="F8" s="164" t="inlineStr">
         <is>
           <t>静岡</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
-      <c r="D9" s="184" t="inlineStr">
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="162" t="inlineStr">
         <is>
           <t>熱海</t>
         </is>
       </c>
-      <c r="E9" s="185" t="n">
+      <c r="E9" s="163" t="n">
         <v>15</v>
       </c>
-      <c r="F9" s="186" t="inlineStr">
+      <c r="F9" s="164" t="inlineStr">
         <is>
           <t>静岡</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
-      <c r="D10" s="184" t="n"/>
-      <c r="E10" s="185" t="n"/>
-      <c r="F10" s="186" t="n"/>
-    </row>
-    <row r="11" ht="13.5" customHeight="1" s="158">
-      <c r="D11" s="184" t="n"/>
-      <c r="E11" s="185" t="n"/>
-      <c r="F11" s="186" t="n"/>
-    </row>
-    <row r="12" ht="13.5" customHeight="1" s="158">
-      <c r="D12" s="184" t="n"/>
-      <c r="E12" s="185" t="n"/>
-      <c r="F12" s="186" t="n"/>
-    </row>
-    <row r="13" ht="13.5" customHeight="1" s="158">
-      <c r="D13" s="184" t="n"/>
-      <c r="E13" s="185" t="n"/>
-      <c r="F13" s="186" t="n"/>
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="D10" s="162" t="n"/>
+      <c r="E10" s="163" t="n"/>
+      <c r="F10" s="164" t="n"/>
+    </row>
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="D11" s="162" t="n"/>
+      <c r="E11" s="163" t="n"/>
+      <c r="F11" s="164" t="n"/>
+    </row>
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="D12" s="162" t="n"/>
+      <c r="E12" s="163" t="n"/>
+      <c r="F12" s="164" t="n"/>
+    </row>
+    <row r="13" ht="13.5" customHeight="1">
+      <c r="D13" s="162" t="n"/>
+      <c r="E13" s="163" t="n"/>
+      <c r="F13" s="164" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2414,130 +2428,130 @@
   <dimension ref="B2:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="12" customWidth="1" style="158" min="4" max="4"/>
-    <col width="14" customWidth="1" style="158" min="5" max="6"/>
-    <col width="12" customWidth="1" style="158" min="7" max="7"/>
-    <col width="14" customWidth="1" style="158" min="8" max="8"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
-      <c r="B2" s="75" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>04_Calculation ― 集計（RawData/Masterを参照）</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="158"/>
-    <row r="4" ht="13.5" customHeight="1" s="158"/>
-    <row r="5" ht="13.5" customHeight="1" s="158">
-      <c r="D5" s="77" t="inlineStr">
+    <row r="3" ht="13.5" customHeight="1"/>
+    <row r="4" ht="13.5" customHeight="1"/>
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>施設別 売上集計</t>
         </is>
       </c>
-      <c r="E5" s="78" t="n"/>
-      <c r="F5" s="78" t="n"/>
-      <c r="G5" s="78" t="n"/>
-      <c r="H5" s="78" t="n"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" s="158"/>
-    <row r="7" ht="13.5" customHeight="1" s="158">
-      <c r="D7" s="168" t="inlineStr">
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+      <c r="G5" s="67" t="n"/>
+      <c r="H5" s="67" t="n"/>
+    </row>
+    <row r="6" ht="13.5" customHeight="1"/>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>施設</t>
         </is>
       </c>
-      <c r="E7" s="168" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>売上計(円)</t>
         </is>
       </c>
-      <c r="F7" s="154" t="inlineStr">
+      <c r="F7" s="138" t="inlineStr">
         <is>
           <t>売上構成%</t>
         </is>
       </c>
-      <c r="G7" s="168" t="inlineStr">
+      <c r="G7" s="68" t="inlineStr">
         <is>
           <t>客室数(室)</t>
         </is>
       </c>
-      <c r="H7" s="168" t="inlineStr">
+      <c r="H7" s="68" t="inlineStr">
         <is>
           <t>1室売上(円)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
-      <c r="D8" s="80" t="inlineStr">
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="D8" s="69" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="E8" s="96">
+      <c r="E8" s="85">
         <f>SUMIFS('02_RawData'!$I$8:$I$17,'02_RawData'!$E$8:$E$17,D8)</f>
         <v/>
       </c>
-      <c r="F8" s="190">
+      <c r="F8" s="192">
         <f>E8/$E$10</f>
         <v/>
       </c>
-      <c r="G8" s="96">
+      <c r="G8" s="85">
         <f>SUMIFS('03_Master'!$E$8:$E$9,'03_Master'!$D$8:$D$9,D8)</f>
         <v/>
       </c>
-      <c r="H8" s="81">
+      <c r="H8" s="70">
         <f>E8/G8</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
-      <c r="D9" s="139" t="inlineStr">
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="123" t="inlineStr">
         <is>
           <t>熱海</t>
         </is>
       </c>
-      <c r="E9" s="123">
+      <c r="E9" s="108">
         <f>SUMIFS('02_RawData'!$I$8:$I$17,'02_RawData'!$E$8:$E$17,D9)</f>
         <v/>
       </c>
-      <c r="F9" s="191">
+      <c r="F9" s="193">
         <f>E9/$E$10</f>
         <v/>
       </c>
-      <c r="G9" s="123">
+      <c r="G9" s="108">
         <f>SUMIFS('03_Master'!$E$8:$E$9,'03_Master'!$D$8:$D$9,D9)</f>
         <v/>
       </c>
-      <c r="H9" s="170">
+      <c r="H9" s="149">
         <f>E9/G9</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
-      <c r="D10" s="171" t="inlineStr">
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="D10" s="112" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="E10" s="135">
+      <c r="E10" s="119">
         <f>SUM(E8:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="192">
+      <c r="F10" s="194">
         <f>E10/$E$10</f>
         <v/>
       </c>
-      <c r="G10" s="135">
+      <c r="G10" s="119">
         <f>SUM(G8:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="135" t="n"/>
-    </row>
-    <row r="11" ht="13.5" customHeight="1" s="158"/>
-    <row r="12" ht="13.5" customHeight="1" s="158"/>
-    <row r="13" ht="13.5" customHeight="1" s="158"/>
+      <c r="H10" s="119" t="n"/>
+    </row>
+    <row r="11" ht="13.5" customHeight="1"/>
+    <row r="12" ht="13.5" customHeight="1"/>
+    <row r="13" ht="13.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2552,80 +2566,80 @@
   <dimension ref="B2:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="16" customWidth="1" style="158" min="4" max="5"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="16" customWidth="1" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
-      <c r="B2" s="75" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>05_Output ― KPI（Calculationを参照）</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="158"/>
-    <row r="4" ht="13.5" customHeight="1" s="158"/>
-    <row r="5" ht="13.5" customHeight="1" s="158">
-      <c r="D5" s="77" t="inlineStr">
+    <row r="3" ht="13.5" customHeight="1"/>
+    <row r="4" ht="13.5" customHeight="1"/>
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>主要KPI</t>
         </is>
       </c>
-      <c r="E5" s="78" t="n"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" s="158"/>
-    <row r="7" ht="13.5" customHeight="1" s="158">
-      <c r="D7" s="168" t="inlineStr">
+      <c r="E5" s="67" t="n"/>
+    </row>
+    <row r="6" ht="13.5" customHeight="1"/>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="E7" s="168" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>値</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
-      <c r="D8" s="126" t="inlineStr">
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="D8" s="111" t="inlineStr">
         <is>
           <t>総売上(円)</t>
         </is>
       </c>
-      <c r="E8" s="141">
+      <c r="E8" s="125">
         <f>'04_Calculation'!E10</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="125" t="n"/>
-    </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
-      <c r="D10" s="80" t="inlineStr">
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="109" t="n"/>
+      <c r="E9" s="110" t="n"/>
+    </row>
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="D10" s="69" t="inlineStr">
         <is>
           <t>西伊豆 構成比</t>
         </is>
       </c>
-      <c r="E10" s="193">
+      <c r="E10" s="195">
         <f>'04_Calculation'!F8</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1" s="158">
-      <c r="D11" s="85" t="inlineStr">
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="D11" s="74" t="inlineStr">
         <is>
           <t>熱海 構成比</t>
         </is>
       </c>
-      <c r="E11" s="194">
+      <c r="E11" s="196">
         <f>'04_Calculation'!F9</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1" s="158"/>
-    <row r="13" ht="13.5" customHeight="1" s="158"/>
-    <row r="14" ht="13.5" customHeight="1" s="158"/>
+    <row r="12" ht="13.5" customHeight="1"/>
+    <row r="13" ht="13.5" customHeight="1"/>
+    <row r="14" ht="13.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2640,132 +2654,132 @@
   <dimension ref="B2:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="28" customWidth="1" style="158" min="4" max="4"/>
-    <col width="14" customWidth="1" style="158" min="5" max="7"/>
-    <col width="10" customWidth="1" style="158" min="8" max="8"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
-      <c r="B2" s="75" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>06_Check ― 整合性チェック</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="158"/>
-    <row r="4" ht="13.5" customHeight="1" s="158">
+    <row r="3" ht="13.5" customHeight="1"/>
+    <row r="4" ht="13.5" customHeight="1">
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>判定がすべてOKなら、集計は元データと整合。1つでも要確認なら原因を追う。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1" s="158">
-      <c r="D5" s="77" t="inlineStr">
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>チェック項目</t>
         </is>
       </c>
-      <c r="E5" s="78" t="n"/>
-      <c r="F5" s="78" t="n"/>
-      <c r="G5" s="78" t="n"/>
-      <c r="H5" s="78" t="n"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" s="158"/>
-    <row r="7" ht="13.5" customHeight="1" s="158">
-      <c r="D7" s="168" t="inlineStr">
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+      <c r="G5" s="67" t="n"/>
+      <c r="H5" s="67" t="n"/>
+    </row>
+    <row r="6" ht="13.5" customHeight="1"/>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>チェック項目</t>
         </is>
       </c>
-      <c r="E7" s="168" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>値A</t>
         </is>
       </c>
-      <c r="F7" s="168" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>値B</t>
         </is>
       </c>
-      <c r="G7" s="168" t="n"/>
-      <c r="H7" s="168" t="inlineStr">
+      <c r="G7" s="68" t="n"/>
+      <c r="H7" s="68" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
-      <c r="D8" s="80" t="inlineStr">
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="D8" s="69" t="inlineStr">
         <is>
           <t>元データ件数 = 集計対象件数</t>
         </is>
       </c>
-      <c r="E8" s="179">
+      <c r="E8" s="157">
         <f>COUNTA('02_RawData'!$D$8:$D$17)</f>
         <v/>
       </c>
-      <c r="F8" s="177" t="n">
+      <c r="F8" s="155" t="n">
         <v>10</v>
       </c>
-      <c r="G8" s="195">
+      <c r="G8" s="197">
         <f>F8-E8</f>
         <v/>
       </c>
-      <c r="H8" s="98">
+      <c r="H8" s="87">
         <f>IF(G8&lt;0.0001,"OK","要確認")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
-      <c r="D9" s="83" t="inlineStr">
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="72" t="inlineStr">
         <is>
           <t>施設別売上合計 = 総売上</t>
         </is>
       </c>
-      <c r="E9" s="119">
+      <c r="E9" s="105">
         <f>'04_Calculation'!E8+'04_Calculation'!E9</f>
         <v/>
       </c>
-      <c r="F9" s="119">
+      <c r="F9" s="105">
         <f>'04_Calculation'!E10</f>
         <v/>
       </c>
-      <c r="G9" s="196">
+      <c r="G9" s="198">
         <f>F9-E9</f>
         <v/>
       </c>
-      <c r="H9" s="99">
+      <c r="H9" s="88">
         <f>IF(G9&lt;0.0001,"OK","要確認")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
-      <c r="D10" s="85" t="inlineStr">
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="D10" s="74" t="inlineStr">
         <is>
           <t>構成比合計 = 100%</t>
         </is>
       </c>
-      <c r="E10" s="197">
+      <c r="E10" s="199">
         <f>'05_Output'!E10+'05_Output'!E11</f>
         <v/>
       </c>
-      <c r="F10" s="198" t="n">
+      <c r="F10" s="200" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="199">
+      <c r="G10" s="201">
         <f>F10-E10</f>
         <v/>
       </c>
-      <c r="H10" s="100">
+      <c r="H10" s="89">
         <f>IF(G10&lt;0.0001,"OK","要確認")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1" s="158"/>
-    <row r="12" ht="13.5" customHeight="1" s="158"/>
-    <row r="13" ht="13.5" customHeight="1" s="158"/>
+    <row r="11" ht="13.5" customHeight="1"/>
+    <row r="12" ht="13.5" customHeight="1"/>
+    <row r="13" ht="13.5" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="H8:H10">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">

--- a/files/excel-mastery-ch3.xlsx
+++ b/files/excel-mastery-ch3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-1605" yWindow="-16320" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="280" windowWidth="17320" windowHeight="10400" tabRatio="773" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="00_Index" sheetId="1" state="visible" r:id="rId1"/>
@@ -559,7 +559,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1055,74 +1055,77 @@
     <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1913,7 +1916,7 @@
           <t>消費税率</t>
         </is>
       </c>
-      <c r="E8" s="191" t="n">
+      <c r="E8" s="192" t="n">
         <v>0.1</v>
       </c>
       <c r="F8" s="68" t="n"/>
@@ -1954,7 +1957,7 @@
           <t>目標稼働率</t>
         </is>
       </c>
-      <c r="E11" s="191" t="n">
+      <c r="E11" s="192" t="n">
         <v>0.7</v>
       </c>
       <c r="F11" s="68" t="n"/>
@@ -2493,7 +2496,7 @@
         <f>SUMIFS('02_RawData'!$I$8:$I$17,'02_RawData'!$E$8:$E$17,D8)</f>
         <v/>
       </c>
-      <c r="F8" s="192">
+      <c r="F8" s="193">
         <f>E8/$E$10</f>
         <v/>
       </c>
@@ -2516,7 +2519,7 @@
         <f>SUMIFS('02_RawData'!$I$8:$I$17,'02_RawData'!$E$8:$E$17,D9)</f>
         <v/>
       </c>
-      <c r="F9" s="193">
+      <c r="F9" s="194">
         <f>E9/$E$10</f>
         <v/>
       </c>
@@ -2539,7 +2542,7 @@
         <f>SUM(E8:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="194">
+      <c r="F10" s="195">
         <f>E10/$E$10</f>
         <v/>
       </c>
@@ -2621,7 +2624,7 @@
           <t>西伊豆 構成比</t>
         </is>
       </c>
-      <c r="E10" s="195">
+      <c r="E10" s="196">
         <f>'04_Calculation'!F8</f>
         <v/>
       </c>
@@ -2632,7 +2635,7 @@
           <t>熱海 構成比</t>
         </is>
       </c>
-      <c r="E11" s="196">
+      <c r="E11" s="197">
         <f>'04_Calculation'!F9</f>
         <v/>
       </c>
@@ -2723,7 +2726,7 @@
       <c r="F8" s="155" t="n">
         <v>10</v>
       </c>
-      <c r="G8" s="197">
+      <c r="G8" s="198">
         <f>F8-E8</f>
         <v/>
       </c>
@@ -2746,7 +2749,7 @@
         <f>'04_Calculation'!E10</f>
         <v/>
       </c>
-      <c r="G9" s="198">
+      <c r="G9" s="199">
         <f>F9-E9</f>
         <v/>
       </c>
@@ -2761,14 +2764,14 @@
           <t>構成比合計 = 100%</t>
         </is>
       </c>
-      <c r="E10" s="199">
+      <c r="E10" s="200">
         <f>'05_Output'!E10+'05_Output'!E11</f>
         <v/>
       </c>
-      <c r="F10" s="200" t="n">
+      <c r="F10" s="201" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="201">
+      <c r="G10" s="202">
         <f>F10-E10</f>
         <v/>
       </c>
